--- a/artfynd/A 45294-2025 artfynd.xlsx
+++ b/artfynd/A 45294-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56071631</v>
+        <v>56071630</v>
       </c>
       <c r="B2" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716762.8258532762</v>
+        <v>716757</v>
       </c>
       <c r="R2" t="n">
-        <v>7058981.188909394</v>
+        <v>7059059</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2015-10-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-10-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,6 +773,417 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>56071629</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78993</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>353</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Storrisberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>716775</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7059089</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2015-10-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2015-10-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>56071631</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storrisberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>716763</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7058981</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2015-10-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2015-10-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>68367199</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storrisberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>716986</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7059055</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-11-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-11-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>68367215</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storrisberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>716988</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7059060</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-11-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-11-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>död gran</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45294-2025 artfynd.xlsx
+++ b/artfynd/A 45294-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56071630</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56071629</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56071631</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68367199</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,8 +1209,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68367215</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>